--- a/total-kharcha.xlsx
+++ b/total-kharcha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\6502-series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E2705F-8E97-4306-A2B5-3198034C0980}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE80EF6-BBD7-4FC0-9E8B-DDF3AF6A0793}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{BBC14CF9-AE7D-4820-AE7A-94E8742D0BAD}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
   <si>
     <t>Total Kharcha on Electronics</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>DIP IC Sockets</t>
+  </si>
+  <si>
+    <t>Solder bit (RETURN)</t>
   </si>
 </sst>
 </file>
@@ -488,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -506,18 +509,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -527,10 +519,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -548,6 +543,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -587,9 +594,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -946,58 +950,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED3FF3E-49C0-4820-85B9-C6E8BE155202}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:XFD62"/>
+  <dimension ref="A1:XFD67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="9">
-        <f>SUM(H13,H21,H29,H51,H62)</f>
-        <v>12483</v>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="25">
+        <f>SUM(H13,H21,H29,H51,H62,H67)</f>
+        <v>12803</v>
       </c>
     </row>
     <row r="2" spans="1:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="10"/>
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:16384" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="48"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="11"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:16384" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
       <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1009,35 +1013,35 @@
       </c>
     </row>
     <row r="5" spans="1:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
     </row>
     <row r="6" spans="1:16384" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
     </row>
     <row r="7" spans="1:16384" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="2">
         <v>1</v>
       </c>
@@ -1050,13 +1054,13 @@
       </c>
     </row>
     <row r="8" spans="1:16384" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
       <c r="F8" s="2">
         <v>1</v>
       </c>
@@ -1069,13 +1073,13 @@
       </c>
     </row>
     <row r="9" spans="1:16384" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="2">
         <v>1</v>
       </c>
@@ -1088,13 +1092,13 @@
       </c>
     </row>
     <row r="10" spans="1:16384" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
       <c r="F10" s="2">
         <v>1</v>
       </c>
@@ -1107,13 +1111,13 @@
       </c>
     </row>
     <row r="11" spans="1:16384" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
       <c r="F11" s="2">
         <v>3</v>
       </c>
@@ -1126,64 +1130,64 @@
       </c>
     </row>
     <row r="12" spans="1:16384" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="53"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="54"/>
       <c r="H12" s="3">
         <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:16384" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="15"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
       <c r="H13" s="8">
         <f>SUM(H7:H12)</f>
         <v>2870</v>
       </c>
     </row>
     <row r="14" spans="1:16384" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
     </row>
     <row r="15" spans="1:16384" x14ac:dyDescent="0.25">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
     </row>
     <row r="16" spans="1:16384" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="45"/>
       <c r="F16" s="5">
         <v>1</v>
       </c>
@@ -1194,13 +1198,13 @@
         <f>G16*F16</f>
         <v>277</v>
       </c>
-      <c r="I16" s="38" t="s">
+      <c r="I16" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
@@ -17574,13 +17578,13 @@
       <c r="XFD16" s="6"/>
     </row>
     <row r="17" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
       <c r="F17" s="2">
         <v>1</v>
       </c>
@@ -17591,23 +17595,23 @@
         <f t="shared" ref="H17:H19" si="1">G17*F17</f>
         <v>720</v>
       </c>
-      <c r="I17" s="38" t="s">
+      <c r="I17" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
     </row>
     <row r="18" spans="1:14" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="44"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="45"/>
       <c r="F18" s="2">
         <v>1</v>
       </c>
@@ -17620,13 +17624,13 @@
       </c>
     </row>
     <row r="19" spans="1:14" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
       <c r="F19" s="5">
         <v>1</v>
       </c>
@@ -17639,65 +17643,65 @@
       </c>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="34"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="36"/>
       <c r="H20" s="3">
         <f>130+100</f>
         <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="37"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="39"/>
       <c r="H21" s="8">
         <f>SUM(H16:H20)</f>
         <v>2433</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="22"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="25"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="24"/>
       <c r="F24" s="2">
         <v>1</v>
       </c>
@@ -17710,13 +17714,13 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="24"/>
       <c r="F25" s="2">
         <v>3</v>
       </c>
@@ -17729,13 +17733,13 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="24"/>
       <c r="F26" s="2">
         <v>2</v>
       </c>
@@ -17748,13 +17752,13 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="2">
         <v>2</v>
       </c>
@@ -17767,13 +17771,13 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="31"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33"/>
       <c r="F28" s="2">
         <v>1</v>
       </c>
@@ -17786,50 +17790,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="15"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="12"/>
       <c r="H29" s="8">
         <f>SUM(H24:H28)</f>
         <v>1290</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="22"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="18"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="25"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="18"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="2">
         <v>1</v>
       </c>
@@ -17842,13 +17846,13 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="18"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="24"/>
       <c r="F33" s="2">
         <v>40</v>
       </c>
@@ -17861,13 +17865,13 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="18"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="24"/>
       <c r="F34" s="2">
         <v>2</v>
       </c>
@@ -17880,13 +17884,13 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="18"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="24"/>
       <c r="F35" s="2">
         <v>2</v>
       </c>
@@ -17899,13 +17903,13 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="18"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="2">
         <v>2</v>
       </c>
@@ -17918,13 +17922,13 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="18"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="24"/>
       <c r="F37" s="2">
         <v>1</v>
       </c>
@@ -17937,13 +17941,13 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
       <c r="F38" s="2">
         <v>2</v>
       </c>
@@ -17956,13 +17960,13 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
       <c r="F39" s="2">
         <v>2</v>
       </c>
@@ -17975,13 +17979,13 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
       <c r="F40" s="2">
         <v>4</v>
       </c>
@@ -17994,13 +17998,13 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
       <c r="F41" s="2">
         <v>2</v>
       </c>
@@ -18013,13 +18017,13 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
       <c r="F42" s="2">
         <v>1</v>
       </c>
@@ -18032,13 +18036,13 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
       <c r="F43" s="2">
         <v>1</v>
       </c>
@@ -18051,13 +18055,13 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
       <c r="F44" s="2">
         <v>5</v>
       </c>
@@ -18070,13 +18074,13 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
       <c r="F45" s="2">
         <v>5</v>
       </c>
@@ -18089,13 +18093,13 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
       <c r="F46" s="2">
         <v>5</v>
       </c>
@@ -18108,13 +18112,13 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
       <c r="F47" s="2">
         <v>1</v>
       </c>
@@ -18127,13 +18131,13 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
       <c r="F48" s="2">
         <v>20</v>
       </c>
@@ -18146,13 +18150,13 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
       <c r="F49" s="2">
         <v>20</v>
       </c>
@@ -18165,13 +18169,13 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
       <c r="F50" s="2">
         <v>1</v>
       </c>
@@ -18184,50 +18188,50 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="15"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="12"/>
       <c r="H51" s="8">
         <f>SUM(H32:H50)</f>
         <v>4650</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="41" t="s">
+      <c r="A52" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="41"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="41"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
       <c r="F54" s="4">
         <v>1</v>
       </c>
@@ -18240,13 +18244,13 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="19" t="s">
+      <c r="A55" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
       <c r="F55" s="4">
         <v>1</v>
       </c>
@@ -18259,13 +18263,13 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
+      <c r="A56" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
       <c r="F56" s="4">
         <v>5</v>
       </c>
@@ -18278,13 +18282,13 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="47" t="s">
+      <c r="A57" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B57" s="47"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="48"/>
       <c r="F57" s="4">
         <v>5</v>
       </c>
@@ -18297,13 +18301,13 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="47" t="s">
+      <c r="A58" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B58" s="47"/>
-      <c r="C58" s="47"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
+      <c r="B58" s="48"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
       <c r="F58" s="4">
         <v>1</v>
       </c>
@@ -18316,13 +18320,13 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="26" t="s">
+      <c r="A59" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="28"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="30"/>
       <c r="F59" s="4">
         <v>1</v>
       </c>
@@ -18335,13 +18339,13 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="26" t="s">
+      <c r="A60" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="28"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="30"/>
       <c r="F60" s="4">
         <v>1</v>
       </c>
@@ -18354,13 +18358,13 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="28"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="30"/>
       <c r="F61" s="4">
         <v>2</v>
       </c>
@@ -18373,34 +18377,108 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="15"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="12"/>
       <c r="H62" s="8">
         <f>SUM(H54:H61)</f>
         <v>1240</v>
       </c>
     </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="14"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="9">
+        <v>2</v>
+      </c>
+      <c r="G65" s="9">
+        <v>250</v>
+      </c>
+      <c r="H65" s="9">
+        <f>G65*F65</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="9">
+        <v>1</v>
+      </c>
+      <c r="G66" s="9">
+        <v>-180</v>
+      </c>
+      <c r="H66" s="9">
+        <f>G66*F66</f>
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="8">
+        <f>SUM(H65:H66)</f>
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A62:G62"/>
+  <mergeCells count="62">
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A52:H53"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:H3"/>
     <mergeCell ref="A5:H6"/>
@@ -18409,37 +18487,12 @@
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="I16:M16"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="A22:H23"/>
-    <mergeCell ref="A14:H15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="I1:I3"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A30:H31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
@@ -18447,6 +18500,36 @@
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="I16:M16"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="A22:H23"/>
+    <mergeCell ref="A14:H15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:H31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A63:H64"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A52:H53"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
